--- a/public/crawlability-manpower-september-2026.xlsx
+++ b/public/crawlability-manpower-september-2026.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של manpower ב-SE Ranking (הסריקה האחרונה: 2026-05-03).</t>
+          <t>להריץ מחדש את ה-Website Audit של manpower ב-SE Ranking (הסריקה האחרונה: 2026-05-03); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. הקישור בעמוד מדיניות הפרטיות נושא את הטקסט 'מדיניות הקוקיז', והכתובת /accessibility שירתה בעבר את עמוד מדיניות הקוקיז (לפי הארכיון, אפריל 2026). לעדכן את הקישור ל-/cookie-policy. בנפרד: לוודא שקיימת באתר הצהרת נגישות מקושרת.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). הקישור בעמוד מדיניות הפרטיות נושא את הטקסט 'מדיניות הקוקיז', והכתובת /accessibility שירתה בעבר את עמוד מדיניות הקוקיז (לפי הארכיון, אפריל 2026). לעדכן את הקישור ל-/cookie-policy. בנפרד: לוודא שקיימת באתר הצהרת נגישות מקושרת.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. הקישור מעמוד /salary_tables מצביע על כתובת עברית שאינה קיימת; עמוד טבלאות השכר הקנוני הוא /salary-tables.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). הקישור מעמוד /salary_tables מצביע על כתובת עברית שאינה קיימת; עמוד טבלאות השכר הקנוני הוא /salary-tables.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">

--- a/public/crawlability-manpower-september-2026.xlsx
+++ b/public/crawlability-manpower-september-2026.xlsx
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">

--- a/public/crawlability-manpower-september-2026.xlsx
+++ b/public/crawlability-manpower-september-2026.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 4 כתובות שמחזירות שגיאה, או לתקן את העמודים (במדגם של 291 כתובות שנבדקו; ייתכנו כתובות נוספות).</t>
+          <t>להסיר ממפת האתר 4 כתובות שמחזירות שגיאה, או לתקן את העמודים (במדגם של 250 מתוך 1201 הכתובות שאינן בסריקה; ייתכנו כתובות נוספות).</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 4 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד (במדגם של 291 כתובות שנבדקו; ייתכנו כתובות נוספות).</t>
+          <t>להסיר ממפת האתר 4 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד (במדגם של 250 מתוך 1201 הכתובות שאינן בסריקה; ייתכנו כתובות נוספות).</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-manpower-september-2026.xlsx
+++ b/public/crawlability-manpower-september-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 2 כתובות (הבולטת: https://www.manpower.co.il/accessibility, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): 2 כתובות; הבולטת https://www.manpower.co.il/accessibility (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות (הבולטת: https://manpower.co.il/cookie-policy, 133 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות; הבולטת https://manpower.co.il/cookie-policy (133 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: כתובת אחת (הבולטת: https://www.manpower.co.il/article/קורות-חיים/, 6 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: כתובת אחת; הבולטת https://www.manpower.co.il/article/קורות-חיים/ (6 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של manpower ב-SE Ranking (הסריקה האחרונה: 2026-05-03); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של manpower ב-SE Ranking; הסריקה האחרונה: 2026-05-03.</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). הקישור בעמוד מדיניות הפרטיות נושא את הטקסט 'מדיניות הקוקיז', והכתובת /accessibility שירתה בעבר את עמוד מדיניות הקוקיז (לפי הארכיון, אפריל 2026). לעדכן את הקישור ל-/cookie-policy. בנפרד: לוודא שקיימת באתר הצהרת נגישות מקושרת.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). הקישור בעמוד מדיניות הפרטיות נושא את הטקסט 'מדיניות הקוקיז', והכתובת /accessibility שירתה בעבר את עמוד מדיניות הקוקיז (לפי הארכיון, אפריל 2026). לעדכן את הקישור ל-/cookie-policy. בנפרד: לוודא שקיימת באתר הצהרת נגישות מקושרת.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). הקישור מעמוד /salary_tables מצביע על כתובת עברית שאינה קיימת; עמוד טבלאות השכר הקנוני הוא /salary-tables.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). הקישור מעמוד /salary_tables מצביע על כתובת עברית שאינה קיימת; עמוד טבלאות השכר הקנוני הוא /salary-tables.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">

--- a/public/crawlability-manpower-september-2026.xlsx
+++ b/public/crawlability-manpower-september-2026.xlsx
@@ -42,7 +42,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +71,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
@@ -92,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -109,13 +104,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -534,7 +526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 2 כתובות; הבולטת https://www.manpower.co.il/accessibility (קישור נכנס אחד).</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת; הבולטת https://www.manpower.co.il/accessibility (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -542,14 +534,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 4 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד (במדגם של 250 מתוך 1201 הכתובות שאינן בסריקה; ייתכנו כתובות נוספות).</t>
+          <t>כתובות שבורות (404): כתובת אחת; הבולטת https://www.manpower.co.il/טבלאות-שכר (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -564,7 +556,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>campaigns.manpower.co.il: מארח עותק של אתר הבית לצד עמודי נחיתה (7 כתובות באינדקס). לוודא canonical לדומיין הראשי בעותק, או noindex.</t>
+          <t>להסיר ממפת האתר 4 כתובות שמפנות (301/302) (במדגם של 250 מתוך 1201 הכתובות שאינן בסריקה; ייתכנו כתובות נוספות).</t>
         </is>
       </c>
     </row>
@@ -579,7 +571,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>professional.manpower.co.il: עותק מלא של אתר הבית, מוגן רק ב-canonical. להגן בסיסמה או להגדיר noindex; לברר את ייעודו.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות; הבולטת https://manpower.co.il/cookie-policy (133 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -587,74 +579,14 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות; הבולטת https://manpower.co.il/cookie-policy (133 קישורים נכנסים).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>להסיר 62 רשומות כפולות ממפת האתר.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
           <t>קישורים פנימיים ללא לוכסן סופי: כתובת אחת; הבולטת https://www.manpower.co.il/article/קורות-חיים/ (6 קישורים נכנסים).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של manpower ב-SE Ranking; הסריקה האחרונה: 2026-05-03.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>post8877.manpower.co.il: ממשק ניהול רשת חשוף לאינטרנט; להעביר לצוות IT לבדיקת חשיפה.</t>
         </is>
       </c>
     </row>
@@ -669,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -743,9 +675,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/accessibility</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.manpower.co.il/טבלאות-שכר</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -763,9 +695,9 @@
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/privacy pol</t>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.manpower.co.il/salary_tables</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -775,62 +707,15 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). הקישור בעמוד מדיניות הפרטיות נושא את הטקסט 'מדיניות הקוקיז', והכתובת /accessibility שירתה בעבר את עמוד מדיניות הקוקיז (לפי הארכיון, אפריל 2026). לעדכן את הקישור ל-/cookie-policy. בנפרד: לוודא שקיימת באתר הצהרת נגישות מקושרת.</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/cookie-policy</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). הקישור מעמוד /salary_tables מצביע על כתובת עברית שאינה קיימת; עמוד טבלאות השכר הקנוני הוא /salary-tables.</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.manpower.co.il/salary-tables</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/טבלאות-שכר</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/salary_tables</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). הקישור מעמוד /salary_tables מצביע על כתובת עברית שאינה קיימת; עמוד טבלאות השכר הקנוני הוא /salary-tables.</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/salary-tables</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
@@ -921,7 +806,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://manpower.co.il/cookie-policy</t>
         </is>
@@ -934,7 +819,7 @@
           <t>308 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/cookie-policy</t>
         </is>
@@ -945,7 +830,7 @@
       <c r="F2" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/
 https://www.manpower.co.il/employers-solutions/service-center
@@ -970,7 +855,7 @@
           <t>קישור פנימי לגרסת דומיין לא קנונית (www/ללא www או http). לעדכן את הקישור לכתובת הקנונית.</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/cookie-policy</t>
         </is>
@@ -982,7 +867,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>http://www.manpower.co.il/</t>
         </is>
@@ -995,7 +880,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/</t>
         </is>
@@ -1006,7 +891,7 @@
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/cookie-policy</t>
         </is>
@@ -1021,7 +906,7 @@
           <t>קישור פנימי לכתובת http שמפנה ל-https. לעדכן את הקישור לכתובת ה-https.</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/</t>
         </is>
@@ -1033,7 +918,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/article/קורות-חיים/</t>
         </is>
@@ -1046,7 +931,7 @@
           <t>308 -&gt; 200</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/article/קורות-חיים</t>
         </is>
@@ -1057,7 +942,7 @@
       <c r="F4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/article/חיפוש-עבודה</t>
         </is>
@@ -1072,7 +957,7 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/article/קורות-חיים</t>
         </is>
@@ -1168,7 +1053,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/my/login</t>
         </is>
@@ -1188,7 +1073,7 @@
       <c r="F2" s="2" t="n">
         <v>399</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/
 https://www.manpower.co.il/employers-solutions/service-center
@@ -1214,14 +1099,14 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/my/dashboard/smartAgent</t>
         </is>
@@ -1241,7 +1126,7 @@
       <c r="F3" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/
 https://www.manpower.co.il/search?JOBEXPERTISE=4177
@@ -1267,14 +1152,14 @@
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/cdn-cgi/l/email-protection</t>
         </is>
@@ -1294,7 +1179,7 @@
       <c r="F4" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/article/קורות-חיים
 https://www.manpower.co.il/article/עבודה-מהבית
@@ -1397,7 +1282,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/sitemap.xml</t>
         </is>
@@ -1451,7 +1336,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/sitemap.xml</t>
         </is>
@@ -1495,12 +1380,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/job/243201</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/search</t>
         </is>
@@ -1517,7 +1402,7 @@
           <t>קוד 404</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/en/about-us/אודות</t>
         </is>
@@ -1535,7 +1420,7 @@
           <t>קוד 404</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/en/article/success-story-cleanroom-maintenance-management-for-israel-aerospace-industries-success-story-iai-cleanroom-excellence</t>
         </is>
@@ -1553,12 +1438,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/job/239839</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/search</t>
         </is>
@@ -1575,12 +1460,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/job/240072</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/search</t>
         </is>
@@ -1597,12 +1482,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/job/239574</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/search</t>
         </is>
@@ -1619,7 +1504,7 @@
           <t>קוד 500</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/article/זכויות-סוציאליות-כל-מה-שמגיע-לכם-לקבל-ב</t>
         </is>
@@ -1637,7 +1522,7 @@
           <t>קוד 404</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/en/employers-solutions/אנגלית-ניהול-לוגיסטיקה-במיקור-חוץ</t>
         </is>
@@ -1655,7 +1540,7 @@
           <t>קוד 301 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il</t>
         </is>
@@ -1673,7 +1558,7 @@
           <t>קוד 0 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/my/dashboard/smartAgent</t>
         </is>
@@ -1691,7 +1576,7 @@
           <t>קוד 0 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/my/login</t>
         </is>
@@ -1709,7 +1594,7 @@
           <t>קוד 308 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/article/קורות-חיים</t>
         </is>
@@ -1722,7 +1607,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/</t>
         </is>
@@ -1732,7 +1617,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/ (0 הפניות)</t>
         </is>
@@ -1744,7 +1629,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>http://www.manpower.co.il/</t>
         </is>
@@ -1754,7 +1639,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/ (1 הפניות)</t>
         </is>
@@ -1766,7 +1651,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>https://manpower.co.il/</t>
         </is>
@@ -1776,7 +1661,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/ (1 הפניות)</t>
         </is>
@@ -1788,7 +1673,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>http://manpower.co.il/</t>
         </is>
@@ -1798,7 +1683,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/ (2 הפניות)</t>
         </is>
@@ -1851,7 +1736,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>https://www.manpower.co.il/</t>
         </is>
@@ -1869,7 +1754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1933,7 +1818,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>campaigns.manpower.co.il</t>
+          <t>leasewise.manpower.co.il</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1943,154 +1828,25 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Manpower - מנפאואר ישראל - ניהול משאבי אנוש וגיוס עובדים</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>index,follow</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Carpro - user login</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>עותק אתר לקמפיינים (index, follow)</t>
+          <t>מסך התחברות</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>מארח עותק של אתר הבית לצד עמודי נחיתה (7 כתובות באינדקס). לוודא canonical לדומיין הראשי בעותק, או noindex.</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>leasewise.manpower.co.il</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Carpro - user login</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>מסך התחברות</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>post8877.manpower.co.il</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>FortiGate</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>ממשק FortiGate</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ממשק ניהול רשת חשוף לאינטרנט; להעביר לצוות IT לבדיקת חשיפה.</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>professional.manpower.co.il</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Manpower - מנפאואר ישראל - ניהול משאבי אנוש וגיוס עובדים</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>index,follow</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>https://www.manpower.co.il/</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>עותק של האתר (index, follow)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>עותק מלא של אתר הבית, מוגן רק ב-canonical. להגן בסיסמה או להגדיר noindex; לברר את ייעודו.</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
         </is>
       </c>
     </row>
